--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2024,6 +2024,46 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cfg.TbNpc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>npc.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NPC表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2064,6 +2064,86 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cfg.TbDialogue</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dialogue</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>dialogue.csv</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>对话头表</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>cfg.TbDialogueNode</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DialogueNode</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>dialoguenode.csv</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>对话节点表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2144,6 +2144,86 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>cfg.TbQuest</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quest</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>quest.csv</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>任务表</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cfg.TbQuestObjective</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>QuestObjective</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>questobjective.csv</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>任务目标表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2224,6 +2224,46 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>cfg.TbLocalization</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>localization.csv</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>本地化词条表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2264,6 +2264,82 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cfg.TbCompanion</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>companion.xlsx</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>队友人设卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cfg.TbCompanionBark</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CompanionBark</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>companionbark.xlsx</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>队友本地台词表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2323,7 +2323,6 @@
           <t>companionbark.xlsx</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>list</t>
@@ -2337,6 +2336,41 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>队友本地台词表</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>cfg.TbAudio</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>audio.xlsx</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2374,6 +2374,46 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>cfg.TbSkill</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>技能树表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -2414,6 +2414,166 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>cfg.TbCompanionAffinityTier</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CompanionAffinityTier</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tier@companionaffinity.xlsx</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>好感档位表</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cfg.TbCompanionAffinityGain</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CompanionAffinityGain</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Gain@companionaffinity.xlsx</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>好感获取规则表</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>cfg.TbCompanionPersona</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CompanionPersona</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>companionpersona.xlsx</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>队友分档人格提示表</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>cfg.TbCompanionMemoryRule</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CompanionMemoryRule</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>companionmemoryrule.xlsx</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>队友记忆规则表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
